--- a/fifa_u20_player_reports.xlsx
+++ b/fifa_u20_player_reports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvarolopezmolina/Desktop/alnassracademy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C6595-9E23-454E-BCA8-44A32D71E0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA0701C-61D9-604A-80AC-4395FF279C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="234">
   <si>
     <t>Date</t>
   </si>
@@ -662,6 +662,66 @@
   </si>
   <si>
     <t>Right-footed winger playing on his natural side, though more of a playmaker or attacking midfielder than a pure winger. Often left the flank to Loke, but at times appeared wide — as in the 1–1 goal, where he started inside, combined well, drifted out to the right and delivered the cross for Brooke-Smith to finish. Highly mobile, roams across the pitch, comfortable in both channels. Suited to play behind the striker.</t>
+  </si>
+  <si>
+    <t>O. Okoro</t>
+  </si>
+  <si>
+    <t>Left-footed left-back with great stamina. Another strong performance, showing very good decision-making and vision. Combined well with the No.7 in the move that led to the 1–0, providing a clever pass before the final cross. Looks like a very solid full-back.</t>
+  </si>
+  <si>
+    <t>Salihu Nasiru</t>
+  </si>
+  <si>
+    <t>Right-footed attacking midfielder with excellent late runs into the box. Twice in the opening 10 minutes he arrived from deep to head the ball. Good in link-up play, technically sound, also takes set pieces, but above all his standout quality is his timing and presence arriving from the second line.</t>
+  </si>
+  <si>
+    <t>S. Suleiman</t>
+  </si>
+  <si>
+    <t>Right-footed winger playing on the left. Very involved, linking up well inside and delivering quality crosses. Showed mobility, often cutting inside to make the No.9 available for assists. Also on set pieces. Has some 1v1 skills, but overall more associative than a pure dribbler.</t>
+  </si>
+  <si>
+    <t>Right-footed striker, comfortable with both feet. Once again had the best chances for his team but couldn't convert any. Especially dangerous in the first half, with a clear one-on-one chance after running onto a through ball, though his left-foot shot resulted in bookings for defenders. Good involvement overall until he was substituted.</t>
+  </si>
+  <si>
+    <t>Left-footed winger playing on the right. Set-piece taker. An explosive player with dribbling ability, though less consistent than in the first game. When he runs at defenders, however, he is highly unpredictable and dangerous.</t>
+  </si>
+  <si>
+    <t>Hamed Yousef</t>
+  </si>
+  <si>
+    <t>Left-footed goalkeeper with very good distribution, comfortable with both feet. Excellent long kicking, including a long free-kick from his own half that led to Suleiman's header under the posts, with little chance on the goals conceded. Produced a top save to deny Nigeria's No.9 at close range.</t>
+  </si>
+  <si>
+    <t>M. Barnawi</t>
+  </si>
+  <si>
+    <t>Right-footed centre-back with strong ball distribution. Good technique and vision, regularly looking for long passes to stretch play. One precise pass fell to the No.8 who headed the goal for 2–2. A valuable outlet for his team in possession.</t>
+  </si>
+  <si>
+    <t>Amar Al-Yuhaybi</t>
+  </si>
+  <si>
+    <t>Right-footed winger playing on the left. The standout player of this team. Scored the 1–1 after beating Nigeria's right-back and coming inside, linking up, and delivering quality crosses. Produced an excellent solo run that was reviewed by VAR for a possible penalty. A winger with good decision-making who constantly creates danger.</t>
+  </si>
+  <si>
+    <t>Ziyad Al Ghamdi</t>
+  </si>
+  <si>
+    <t>Left-footed winger playing on the right. Substituted at half-time but showed plenty of quality in the first half: lively, skilful dribbler, always looking to take on his man. Entertaining to watch, though his small frame means he struggles physically and often fails to make the most of the chances he creates. Technically gifted, though needs to add more end product.</t>
+  </si>
+  <si>
+    <t>Talal Haji</t>
+  </si>
+  <si>
+    <t>Left-footed striker who came on at half-time and made a strong impact. A reference point up front, able to run in behind, hold the ball up and link play. Scored the 2–2 with a delicate, well-placed header from Barnawi's long ball. Still has just 20 yards to run in behind. Gave his team much more presence up front than Al-Khaibri.</t>
+  </si>
+  <si>
+    <t>Arabia Saudita</t>
+  </si>
+  <si>
+    <t>Nigeria vs Arabia Saudita</t>
   </si>
 </sst>
 </file>
@@ -750,20 +810,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1066,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1133,40 +1190,40 @@
       <c r="B2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="1">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="6">
-        <v>4</v>
-      </c>
-      <c r="J2" s="6">
+      <c r="I2" s="1">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1">
         <v>4</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="5">
         <v>90</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1177,40 +1234,40 @@
       <c r="B3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="1">
         <v>11</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="6">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6">
+      <c r="I3" s="1">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1">
         <v>4</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="5">
         <v>90</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1221,40 +1278,40 @@
       <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="1">
         <v>18</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6">
-        <v>4</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="I4" s="1">
+        <v>4</v>
+      </c>
+      <c r="J4" s="1">
         <v>4</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M4" s="5">
         <v>90</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1265,40 +1322,40 @@
       <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="1">
         <v>6</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="6">
-        <v>5</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="1">
+        <v>5</v>
+      </c>
+      <c r="J5" s="1">
         <v>4</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="5">
         <v>45</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1309,40 +1366,40 @@
       <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="1">
         <v>11</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="6">
-        <v>5</v>
-      </c>
-      <c r="J6" s="6">
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1">
         <v>4</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="6" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="5">
         <v>45</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1353,40 +1410,40 @@
       <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="1">
         <v>7</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="6">
-        <v>4</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="I7" s="1">
+        <v>4</v>
+      </c>
+      <c r="J7" s="1">
         <v>4</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="5">
         <v>90</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1397,34 +1454,34 @@
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="1">
         <v>10</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="6">
-        <v>5</v>
-      </c>
-      <c r="J8" s="6">
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1">
         <v>5</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M8" s="5">
@@ -1441,3007 +1498,3447 @@
       <c r="B9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="6">
-        <v>19</v>
-      </c>
-      <c r="H9" s="6" t="s">
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="6">
-        <v>4</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="I9" s="1">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1">
         <v>5</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="5">
         <v>90</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>45928</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="1">
         <v>8</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="1">
         <v>3</v>
       </c>
-      <c r="J10" s="6">
-        <v>4</v>
-      </c>
-      <c r="K10" s="6" t="s">
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M10" s="5">
         <v>90</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>45928</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="6">
-        <v>5</v>
-      </c>
-      <c r="J11" s="6">
-        <v>4</v>
-      </c>
-      <c r="K11" s="6" t="s">
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>4</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M11" s="5">
         <v>90</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>45928</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="1">
         <v>11</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="6">
-        <v>4</v>
-      </c>
-      <c r="J12" s="6">
-        <v>4</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="I12" s="1">
+        <v>4</v>
+      </c>
+      <c r="J12" s="1">
+        <v>4</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M12" s="5">
         <v>90</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>45928</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="1">
         <v>20</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="6">
-        <v>4</v>
-      </c>
-      <c r="J13" s="6">
-        <v>4</v>
-      </c>
-      <c r="K13" s="6" t="s">
+      <c r="I13" s="1">
+        <v>4</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="6">
         <v>45</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>45928</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="6" t="s">
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="1">
         <v>9</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="6">
-        <v>4</v>
-      </c>
-      <c r="J14" s="6">
-        <v>5</v>
-      </c>
-      <c r="K14" s="6" t="s">
+      <c r="I14" s="1">
+        <v>4</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="6">
         <v>45</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>45928</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="6">
-        <v>4</v>
-      </c>
-      <c r="J15" s="6">
-        <v>4</v>
-      </c>
-      <c r="K15" s="6" t="s">
+      <c r="I15" s="1">
+        <v>4</v>
+      </c>
+      <c r="J15" s="1">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="7">
-        <v>90</v>
-      </c>
-      <c r="N15" s="6" t="s">
+      <c r="L15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="6">
+        <v>90</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>45928</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="6" t="s">
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="1">
         <v>10</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="6">
-        <v>4</v>
-      </c>
-      <c r="J16" s="6">
-        <v>4</v>
-      </c>
-      <c r="K16" s="6" t="s">
+      <c r="I16" s="1">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="7">
-        <v>90</v>
-      </c>
-      <c r="N16" s="6" t="s">
+      <c r="L16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="6">
+        <v>90</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>45928</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="6">
-        <v>4</v>
-      </c>
-      <c r="J17" s="6">
-        <v>4</v>
-      </c>
-      <c r="K17" s="6" t="s">
+      <c r="I17" s="1">
+        <v>4</v>
+      </c>
+      <c r="J17" s="1">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" s="7">
-        <v>90</v>
-      </c>
-      <c r="N17" s="6" t="s">
+      <c r="L17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="6">
+        <v>90</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>45928</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="1">
         <v>11</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="1">
         <v>3</v>
       </c>
-      <c r="J18" s="6">
-        <v>4</v>
-      </c>
-      <c r="K18" s="6" t="s">
+      <c r="J18" s="1">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="7">
-        <v>90</v>
-      </c>
-      <c r="N18" s="6" t="s">
+      <c r="L18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="6">
+        <v>90</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>45928</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="B19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="1">
         <v>9</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="6">
-        <v>5</v>
-      </c>
-      <c r="J19" s="6">
-        <v>5</v>
-      </c>
-      <c r="K19" s="6" t="s">
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="7">
-        <v>90</v>
-      </c>
-      <c r="N19" s="6" t="s">
+      <c r="L19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="6">
+        <v>90</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <v>45928</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="6">
-        <v>4</v>
-      </c>
-      <c r="H20" s="6" t="s">
+      <c r="G20" s="1">
+        <v>4</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="6">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6">
-        <v>4</v>
-      </c>
-      <c r="K20" s="6" t="s">
+      <c r="I20" s="1">
+        <v>4</v>
+      </c>
+      <c r="J20" s="1">
+        <v>4</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="9">
-        <v>90</v>
-      </c>
-      <c r="N20" s="6" t="s">
+      <c r="L20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="2">
+        <v>90</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>45928</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G21" s="6">
-        <v>15</v>
-      </c>
-      <c r="H21" s="6" t="s">
+      <c r="G21" s="1">
+        <v>15</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="6">
-        <v>4</v>
-      </c>
-      <c r="J21" s="6">
-        <v>4</v>
-      </c>
-      <c r="K21" s="6" t="s">
+      <c r="I21" s="1">
+        <v>4</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="9">
-        <v>90</v>
-      </c>
-      <c r="N21" s="6" t="s">
+      <c r="L21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="2">
+        <v>90</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <v>45928</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="6" t="s">
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="1">
         <v>3</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="6">
-        <v>4</v>
-      </c>
-      <c r="J22" s="6">
-        <v>4</v>
-      </c>
-      <c r="K22" s="6" t="s">
+      <c r="I22" s="1">
+        <v>4</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="9">
-        <v>90</v>
-      </c>
-      <c r="N22" s="6" t="s">
+      <c r="L22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="2">
+        <v>90</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <v>45928</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="1">
         <v>7</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I23" s="6">
-        <v>5</v>
-      </c>
-      <c r="J23" s="6">
-        <v>5</v>
-      </c>
-      <c r="K23" s="6" t="s">
+      <c r="I23" s="1">
+        <v>5</v>
+      </c>
+      <c r="J23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M23" s="9">
-        <v>90</v>
-      </c>
-      <c r="N23" s="6" t="s">
+      <c r="L23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="2">
+        <v>90</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
+      <c r="A24" s="7">
         <v>45928</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="6" t="s">
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="1">
         <v>17</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="6">
-        <v>5</v>
-      </c>
-      <c r="J24" s="6">
-        <v>4</v>
-      </c>
-      <c r="K24" s="6" t="s">
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" s="9">
-        <v>90</v>
-      </c>
-      <c r="N24" s="6" t="s">
+      <c r="L24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="2">
+        <v>90</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <v>45928</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="B25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G25" s="6">
-        <v>21</v>
-      </c>
-      <c r="H25" s="6" t="s">
+      <c r="G25" s="1">
+        <v>21</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="6">
-        <v>4</v>
-      </c>
-      <c r="J25" s="6">
-        <v>4</v>
-      </c>
-      <c r="K25" s="6" t="s">
+      <c r="I25" s="1">
+        <v>4</v>
+      </c>
+      <c r="J25" s="1">
+        <v>4</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M25" s="9">
-        <v>90</v>
-      </c>
-      <c r="N25" s="6" t="s">
+      <c r="L25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" s="2">
+        <v>90</v>
+      </c>
+      <c r="N25" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
+      <c r="A26" s="7">
         <v>45928</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="6" t="s">
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="1">
         <v>3</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="6">
-        <v>4</v>
-      </c>
-      <c r="J26" s="6">
-        <v>4</v>
-      </c>
-      <c r="K26" s="6" t="s">
+      <c r="I26" s="1">
+        <v>4</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" s="9">
-        <v>90</v>
-      </c>
-      <c r="N26" s="6" t="s">
+      <c r="L26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="2">
+        <v>90</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="A27" s="7">
         <v>45928</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="1">
         <v>8</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="6">
-        <v>4</v>
-      </c>
-      <c r="J27" s="6">
-        <v>4</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="9">
-        <v>90</v>
-      </c>
-      <c r="N27" s="6" t="s">
+      <c r="I27" s="1">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="2">
+        <v>90</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
+      <c r="A28" s="7">
         <v>45928</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="B28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="1">
         <v>7</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="6">
-        <v>5</v>
-      </c>
-      <c r="J28" s="6">
-        <v>4</v>
-      </c>
-      <c r="K28" s="6" t="s">
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M28" s="9">
-        <v>90</v>
-      </c>
-      <c r="N28" s="6" t="s">
+      <c r="L28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="2">
+        <v>90</v>
+      </c>
+      <c r="N28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="B29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="10">
-        <v>4</v>
-      </c>
-      <c r="J29" s="10">
-        <v>5</v>
-      </c>
-      <c r="K29" s="10" t="s">
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29">
+        <v>5</v>
+      </c>
+      <c r="K29" t="s">
         <v>98</v>
       </c>
-      <c r="L29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="9">
-        <v>90</v>
-      </c>
-      <c r="N29" s="10" t="s">
+      <c r="L29" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" s="2">
+        <v>90</v>
+      </c>
+      <c r="N29" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
+      <c r="A30" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="B30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" t="s">
         <v>95</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" t="s">
         <v>78</v>
       </c>
-      <c r="I30" s="10">
-        <v>4</v>
-      </c>
-      <c r="J30" s="10">
-        <v>4</v>
-      </c>
-      <c r="K30" s="10" t="s">
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30">
+        <v>4</v>
+      </c>
+      <c r="K30" t="s">
         <v>101</v>
       </c>
-      <c r="L30" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M30" s="9">
-        <v>90</v>
-      </c>
-      <c r="N30" s="10" t="s">
+      <c r="L30" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" s="2">
+        <v>90</v>
+      </c>
+      <c r="N30" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+      <c r="A31" t="s">
         <v>93</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="B31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" t="s">
         <v>95</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" t="s">
         <v>103</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="10">
-        <v>4</v>
-      </c>
-      <c r="J31" s="10">
-        <v>4</v>
-      </c>
-      <c r="K31" s="10" t="s">
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31" t="s">
         <v>104</v>
       </c>
-      <c r="L31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M31" s="9">
-        <v>90</v>
-      </c>
-      <c r="N31" s="10" t="s">
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" s="2">
+        <v>90</v>
+      </c>
+      <c r="N31" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
+      <c r="A32" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" t="s">
         <v>95</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" t="s">
         <v>105</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" t="s">
         <v>106</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" t="s">
         <v>27</v>
       </c>
-      <c r="I32" s="10">
-        <v>4</v>
-      </c>
-      <c r="J32" s="10">
-        <v>5</v>
-      </c>
-      <c r="K32" s="10" t="s">
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
+      <c r="K32" t="s">
         <v>107</v>
       </c>
-      <c r="L32" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M32" s="9">
-        <v>90</v>
-      </c>
-      <c r="N32" s="10" t="s">
+      <c r="L32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" s="2">
+        <v>90</v>
+      </c>
+      <c r="N32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
+      <c r="A33" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="B33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" t="s">
         <v>109</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="10">
-        <v>5</v>
-      </c>
-      <c r="J33" s="10">
-        <v>5</v>
-      </c>
-      <c r="K33" s="10" t="s">
+      <c r="I33">
+        <v>5</v>
+      </c>
+      <c r="J33">
+        <v>5</v>
+      </c>
+      <c r="K33" t="s">
         <v>110</v>
       </c>
-      <c r="L33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M33" s="9">
-        <v>90</v>
-      </c>
-      <c r="N33" s="10" t="s">
+      <c r="L33" t="s">
+        <v>19</v>
+      </c>
+      <c r="M33" s="2">
+        <v>90</v>
+      </c>
+      <c r="N33" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="10" t="s">
+      <c r="A34" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="B34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
         <v>94</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" t="s">
         <v>112</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" t="s">
         <v>113</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" t="s">
         <v>75</v>
       </c>
-      <c r="I34" s="10">
-        <v>5</v>
-      </c>
-      <c r="J34" s="10">
-        <v>5</v>
-      </c>
-      <c r="K34" s="10" t="s">
+      <c r="I34">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+      <c r="K34" t="s">
         <v>114</v>
       </c>
-      <c r="L34" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M34" s="9">
-        <v>90</v>
-      </c>
-      <c r="N34" s="10" t="s">
+      <c r="L34" t="s">
+        <v>19</v>
+      </c>
+      <c r="M34" s="2">
+        <v>90</v>
+      </c>
+      <c r="N34" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="A35" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" t="s">
         <v>106</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="10">
-        <v>4</v>
-      </c>
-      <c r="J35" s="10">
-        <v>4</v>
-      </c>
-      <c r="K35" s="10" t="s">
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35" t="s">
         <v>116</v>
       </c>
-      <c r="L35" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M35" s="9">
-        <v>90</v>
-      </c>
-      <c r="N35" s="10" t="s">
+      <c r="L35" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" s="2">
+        <v>90</v>
+      </c>
+      <c r="N35" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="B36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" t="s">
         <v>111</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" t="s">
         <v>117</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" t="s">
         <v>118</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="10">
-        <v>4</v>
-      </c>
-      <c r="J36" s="10">
-        <v>4</v>
-      </c>
-      <c r="K36" s="10" t="s">
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="J36">
+        <v>4</v>
+      </c>
+      <c r="K36" t="s">
         <v>119</v>
       </c>
-      <c r="L36" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M36" s="9">
-        <v>90</v>
-      </c>
-      <c r="N36" s="10" t="s">
+      <c r="L36" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" s="2">
+        <v>90</v>
+      </c>
+      <c r="N36" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
+      <c r="A37" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
         <v>94</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" t="s">
         <v>111</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" t="s">
         <v>120</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" t="s">
         <v>121</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="10">
-        <v>5</v>
-      </c>
-      <c r="J37" s="10">
-        <v>5</v>
-      </c>
-      <c r="K37" s="10" t="s">
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+      <c r="K37" t="s">
         <v>122</v>
       </c>
-      <c r="L37" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="M37" s="9">
-        <v>90</v>
-      </c>
-      <c r="N37" s="10" t="s">
+      <c r="L37" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" s="2">
+        <v>90</v>
+      </c>
+      <c r="N37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
+      <c r="A38" s="7">
         <v>45932</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D38" s="6" t="s">
+      <c r="B38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G38" s="6">
-        <v>4</v>
-      </c>
-      <c r="H38" s="6" t="s">
+      <c r="G38" s="1">
+        <v>4</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="6">
-        <v>4</v>
-      </c>
-      <c r="J38" s="6">
-        <v>4</v>
-      </c>
-      <c r="K38" s="6" t="s">
+      <c r="I38" s="1">
+        <v>4</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M38" s="9">
-        <v>90</v>
-      </c>
-      <c r="N38" s="6" t="s">
+      <c r="L38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="2">
+        <v>90</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
+      <c r="A39" s="7">
         <v>45932</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="6" t="s">
+      <c r="B39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="1">
         <v>17</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I39" s="6">
-        <v>5</v>
-      </c>
-      <c r="J39" s="6">
-        <v>5</v>
-      </c>
-      <c r="K39" s="6" t="s">
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>5</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M39" s="9">
-        <v>90</v>
-      </c>
-      <c r="N39" s="6" t="s">
+      <c r="L39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" s="2">
+        <v>90</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
+      <c r="A40" s="7">
         <v>45932</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="6" t="s">
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="1">
         <v>6</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="H40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I40" s="6">
-        <v>4</v>
-      </c>
-      <c r="J40" s="6">
-        <v>5</v>
-      </c>
-      <c r="K40" s="6" t="s">
+      <c r="I40" s="1">
+        <v>4</v>
+      </c>
+      <c r="J40" s="1">
+        <v>5</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="L40" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M40" s="9">
-        <v>90</v>
-      </c>
-      <c r="N40" s="6" t="s">
+      <c r="L40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" s="2">
+        <v>90</v>
+      </c>
+      <c r="N40" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
+      <c r="A41" s="7">
         <v>45932</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D41" s="6" t="s">
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="1">
         <v>14</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="6">
-        <v>5</v>
-      </c>
-      <c r="J41" s="6">
-        <v>5</v>
-      </c>
-      <c r="K41" s="6" t="s">
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L41" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M41" s="9">
-        <v>90</v>
-      </c>
-      <c r="N41" s="6" t="s">
+      <c r="L41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="2">
+        <v>90</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="8">
+      <c r="A42" s="7">
         <v>45932</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="6" t="s">
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="1">
         <v>20</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="6">
-        <v>5</v>
-      </c>
-      <c r="J42" s="6">
-        <v>4</v>
-      </c>
-      <c r="K42" s="6" t="s">
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="2">
         <v>45</v>
       </c>
-      <c r="N42" s="6" t="s">
+      <c r="N42" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="8">
+      <c r="A43" s="7">
         <v>45932</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D43" s="6" t="s">
+      <c r="B43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="1">
         <v>1</v>
       </c>
-      <c r="H43" s="6" t="s">
+      <c r="H43" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="6">
-        <v>5</v>
-      </c>
-      <c r="J43" s="6">
-        <v>4</v>
-      </c>
-      <c r="K43" s="6" t="s">
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M43" s="9">
-        <v>90</v>
-      </c>
-      <c r="N43" s="6" t="s">
+      <c r="L43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" s="2">
+        <v>90</v>
+      </c>
+      <c r="N43" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="8">
+      <c r="A44" s="7">
         <v>45932</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="6" t="s">
+      <c r="B44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="1">
         <v>10</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="H44" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="6">
-        <v>4</v>
-      </c>
-      <c r="J44" s="6">
-        <v>4</v>
-      </c>
-      <c r="K44" s="6" t="s">
+      <c r="I44" s="1">
+        <v>4</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="2">
         <v>45</v>
       </c>
-      <c r="N44" s="6" t="s">
+      <c r="N44" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="8">
+      <c r="A45" s="7">
         <v>45932</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="B45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="1">
         <v>7</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="H45" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I45" s="6">
-        <v>4</v>
-      </c>
-      <c r="J45" s="6">
-        <v>5</v>
-      </c>
-      <c r="K45" s="6" t="s">
+      <c r="I45" s="1">
+        <v>4</v>
+      </c>
+      <c r="J45" s="1">
+        <v>5</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="L45" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M45" s="9">
-        <v>90</v>
-      </c>
-      <c r="N45" s="6" t="s">
+      <c r="L45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="2">
+        <v>90</v>
+      </c>
+      <c r="N45" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="8">
+      <c r="A46" s="7">
         <v>45932</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="B46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="1">
         <v>11</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H46" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I46" s="6">
-        <v>5</v>
-      </c>
-      <c r="J46" s="6">
-        <v>5</v>
-      </c>
-      <c r="K46" s="6" t="s">
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
+        <v>5</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L46" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M46" s="9">
-        <v>90</v>
-      </c>
-      <c r="N46" s="6" t="s">
+      <c r="L46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M46" s="2">
+        <v>90</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="8">
+      <c r="A47" s="7">
         <v>45932</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="6" t="s">
+      <c r="B47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="1">
         <v>13</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="H47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="6">
-        <v>4</v>
-      </c>
-      <c r="J47" s="6">
-        <v>4</v>
-      </c>
-      <c r="K47" s="6" t="s">
+      <c r="I47" s="1">
+        <v>4</v>
+      </c>
+      <c r="J47" s="1">
+        <v>4</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="L47" s="6" t="s">
+      <c r="L47" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="2">
         <v>45</v>
       </c>
-      <c r="N47" s="6" t="s">
+      <c r="N47" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="8">
+      <c r="A48" s="7">
         <v>45929</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="6" t="s">
+      <c r="C48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="1">
         <v>12</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H48" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I48" s="6">
-        <v>5</v>
-      </c>
-      <c r="J48" s="6">
-        <v>4</v>
-      </c>
-      <c r="K48" s="6" t="s">
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
+        <v>4</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="L48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M48" s="9">
-        <v>90</v>
-      </c>
-      <c r="N48" s="6" t="s">
+      <c r="L48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M48" s="2">
+        <v>90</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O48" s="2"/>
     </row>
     <row r="49" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
+      <c r="A49" s="7">
         <v>45929</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="6" t="s">
+      <c r="C49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G49" s="6">
-        <v>4</v>
-      </c>
-      <c r="H49" s="6" t="s">
+      <c r="G49" s="1">
+        <v>4</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I49" s="6">
-        <v>4</v>
-      </c>
-      <c r="J49" s="6">
-        <v>4</v>
-      </c>
-      <c r="K49" s="6" t="s">
+      <c r="I49" s="1">
+        <v>4</v>
+      </c>
+      <c r="J49" s="1">
+        <v>4</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="L49" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M49" s="9">
-        <v>90</v>
-      </c>
-      <c r="N49" s="6" t="s">
+      <c r="L49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="2">
+        <v>90</v>
+      </c>
+      <c r="N49" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O49" s="2"/>
     </row>
     <row r="50" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="8">
+      <c r="A50" s="7">
         <v>45929</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="6" t="s">
+      <c r="C50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="1">
         <v>3</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="H50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I50" s="6">
-        <v>5</v>
-      </c>
-      <c r="J50" s="6">
-        <v>5</v>
-      </c>
-      <c r="K50" s="6" t="s">
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M50" s="9">
-        <v>90</v>
-      </c>
-      <c r="N50" s="6" t="s">
+      <c r="L50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" s="2">
+        <v>90</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O50" s="2"/>
     </row>
     <row r="51" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="8">
+      <c r="A51" s="7">
         <v>45929</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="6" t="s">
+      <c r="C51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="1">
         <v>6</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="H51" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I51" s="6">
-        <v>4</v>
-      </c>
-      <c r="J51" s="6">
-        <v>4</v>
-      </c>
-      <c r="K51" s="6" t="s">
+      <c r="I51" s="1">
+        <v>4</v>
+      </c>
+      <c r="J51" s="1">
+        <v>4</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="L51" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M51" s="9">
-        <v>90</v>
-      </c>
-      <c r="N51" s="6" t="s">
+      <c r="L51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="2">
+        <v>90</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O51" s="2"/>
     </row>
     <row r="52" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="8">
+      <c r="A52" s="7">
         <v>45929</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="6" t="s">
+      <c r="C52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G52" s="6">
-        <v>15</v>
-      </c>
-      <c r="H52" s="6" t="s">
+      <c r="G52" s="1">
+        <v>15</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I52" s="6">
-        <v>5</v>
-      </c>
-      <c r="J52" s="6">
-        <v>5</v>
-      </c>
-      <c r="K52" s="6" t="s">
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="L52" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M52" s="9">
-        <v>90</v>
-      </c>
-      <c r="N52" s="6" t="s">
+      <c r="L52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M52" s="2">
+        <v>90</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O52" s="2"/>
     </row>
     <row r="53" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="8">
+      <c r="A53" s="7">
         <v>45929</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="6" t="s">
+      <c r="C53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G53" s="6">
-        <v>5</v>
-      </c>
-      <c r="H53" s="6" t="s">
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="6">
-        <v>4</v>
-      </c>
-      <c r="J53" s="6">
-        <v>4</v>
-      </c>
-      <c r="K53" s="6" t="s">
+      <c r="I53" s="1">
+        <v>4</v>
+      </c>
+      <c r="J53" s="1">
+        <v>4</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="L53" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M53" s="9">
-        <v>90</v>
-      </c>
-      <c r="N53" s="6" t="s">
+      <c r="L53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M53" s="2">
+        <v>90</v>
+      </c>
+      <c r="N53" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O53" s="2"/>
     </row>
     <row r="54" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="8">
+      <c r="A54" s="7">
         <v>45929</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D54" s="6" t="s">
+      <c r="C54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="1">
         <v>7</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H54" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I54" s="6">
-        <v>4</v>
-      </c>
-      <c r="J54" s="6">
-        <v>4</v>
-      </c>
-      <c r="K54" s="6" t="s">
+      <c r="I54" s="1">
+        <v>4</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M54" s="9">
-        <v>90</v>
-      </c>
-      <c r="N54" s="6" t="s">
+      <c r="L54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="2">
+        <v>90</v>
+      </c>
+      <c r="N54" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O54" s="2"/>
     </row>
     <row r="55" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="8">
+      <c r="A55" s="7">
         <v>45929</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D55" s="6" t="s">
+      <c r="C55" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G55" s="6">
-        <v>19</v>
-      </c>
-      <c r="H55" s="6" t="s">
+      <c r="G55" s="1">
+        <v>19</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I55" s="6">
+      <c r="I55" s="1">
         <v>3</v>
       </c>
-      <c r="J55" s="6">
-        <v>4</v>
-      </c>
-      <c r="K55" s="6" t="s">
+      <c r="J55" s="1">
+        <v>4</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="L55" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M55" s="9">
-        <v>90</v>
-      </c>
-      <c r="N55" s="6" t="s">
+      <c r="L55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="2">
+        <v>90</v>
+      </c>
+      <c r="N55" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O55" s="2"/>
     </row>
     <row r="56" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="8">
+      <c r="A56" s="7">
         <v>45929</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="6" t="s">
+      <c r="C56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="1">
         <v>13</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H56" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I56" s="6">
-        <v>4</v>
-      </c>
-      <c r="J56" s="6">
-        <v>4</v>
-      </c>
-      <c r="K56" s="6" t="s">
+      <c r="I56" s="1">
+        <v>4</v>
+      </c>
+      <c r="J56" s="1">
+        <v>4</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="L56" s="6" t="s">
+      <c r="L56" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M56" s="9">
+      <c r="M56" s="2">
         <v>45</v>
       </c>
-      <c r="N56" s="6" t="s">
+      <c r="N56" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O56" s="2"/>
     </row>
     <row r="57" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="8">
+      <c r="A57" s="7">
         <v>45929</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" s="6" t="s">
+      <c r="C57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="1">
         <v>11</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="H57" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I57" s="6">
-        <v>5</v>
-      </c>
-      <c r="J57" s="6">
-        <v>5</v>
-      </c>
-      <c r="K57" s="6" t="s">
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>5</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="L57" s="6" t="s">
+      <c r="L57" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M57" s="9">
+      <c r="M57" s="2">
         <v>45</v>
       </c>
-      <c r="N57" s="6" t="s">
+      <c r="N57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O57" s="2"/>
     </row>
     <row r="58" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="8">
+      <c r="A58" s="7">
         <v>45929</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C58" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D58" s="6" t="s">
+      <c r="C58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="1">
         <v>20</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="H58" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I58" s="6">
-        <v>4</v>
-      </c>
-      <c r="J58" s="6">
-        <v>5</v>
-      </c>
-      <c r="K58" s="6" t="s">
+      <c r="I58" s="1">
+        <v>4</v>
+      </c>
+      <c r="J58" s="1">
+        <v>5</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L58" s="6" t="s">
+      <c r="L58" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M58" s="9">
+      <c r="M58" s="2">
         <v>45</v>
       </c>
-      <c r="N58" s="6" t="s">
+      <c r="N58" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O58" s="2"/>
     </row>
     <row r="59" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="8">
+      <c r="A59" s="7">
         <v>45929</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C59" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="6" t="s">
+      <c r="C59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="1">
         <v>1</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="H59" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I59" s="6">
-        <v>4</v>
-      </c>
-      <c r="J59" s="6">
-        <v>4</v>
-      </c>
-      <c r="K59" s="6" t="s">
+      <c r="I59" s="1">
+        <v>4</v>
+      </c>
+      <c r="J59" s="1">
+        <v>4</v>
+      </c>
+      <c r="K59" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L59" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M59" s="9">
-        <v>90</v>
-      </c>
-      <c r="N59" s="6" t="s">
+      <c r="L59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M59" s="2">
+        <v>90</v>
+      </c>
+      <c r="N59" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O59" s="2"/>
     </row>
     <row r="60" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="8">
+      <c r="A60" s="7">
         <v>45929</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="6" t="s">
+      <c r="C60" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F60" s="6" t="s">
+      <c r="F60" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G60" s="6">
-        <v>4</v>
-      </c>
-      <c r="H60" s="6" t="s">
+      <c r="G60" s="1">
+        <v>4</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I60" s="6">
-        <v>4</v>
-      </c>
-      <c r="J60" s="6">
-        <v>5</v>
-      </c>
-      <c r="K60" s="6" t="s">
+      <c r="I60" s="1">
+        <v>4</v>
+      </c>
+      <c r="J60" s="1">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="L60" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M60" s="9">
-        <v>90</v>
-      </c>
-      <c r="N60" s="6" t="s">
+      <c r="L60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M60" s="2">
+        <v>90</v>
+      </c>
+      <c r="N60" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O60" s="2"/>
     </row>
     <row r="61" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="8">
+      <c r="A61" s="7">
         <v>45929</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="6" t="s">
+      <c r="C61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F61" s="6" t="s">
+      <c r="F61" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="1">
         <v>2</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="H61" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I61" s="6">
-        <v>4</v>
-      </c>
-      <c r="J61" s="6">
-        <v>4</v>
-      </c>
-      <c r="K61" s="6" t="s">
+      <c r="I61" s="1">
+        <v>4</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="L61" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M61" s="9">
-        <v>90</v>
-      </c>
-      <c r="N61" s="6" t="s">
+      <c r="L61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M61" s="2">
+        <v>90</v>
+      </c>
+      <c r="N61" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O61" s="2"/>
     </row>
     <row r="62" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="8">
+      <c r="A62" s="7">
         <v>45929</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D62" s="6" t="s">
+      <c r="C62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F62" s="6" t="s">
+      <c r="F62" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="1">
         <v>18</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="H62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I62" s="6">
-        <v>5</v>
-      </c>
-      <c r="J62" s="6">
-        <v>5</v>
-      </c>
-      <c r="K62" s="6" t="s">
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="L62" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M62" s="9">
-        <v>90</v>
-      </c>
-      <c r="N62" s="6" t="s">
+      <c r="L62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M62" s="2">
+        <v>90</v>
+      </c>
+      <c r="N62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O62" s="2"/>
     </row>
     <row r="63" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="8">
+      <c r="A63" s="7">
         <v>45929</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="C63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="F63" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="1">
         <v>8</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="H63" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I63" s="6">
-        <v>4</v>
-      </c>
-      <c r="J63" s="6">
-        <v>4</v>
-      </c>
-      <c r="K63" s="6" t="s">
+      <c r="I63" s="1">
+        <v>4</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L63" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M63" s="9">
-        <v>90</v>
-      </c>
-      <c r="N63" s="6" t="s">
+      <c r="L63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M63" s="2">
+        <v>90</v>
+      </c>
+      <c r="N63" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O63" s="2"/>
     </row>
     <row r="64" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="8">
+      <c r="A64" s="7">
         <v>45929</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D64" s="6" t="s">
+      <c r="C64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E64" s="6" t="s">
+      <c r="E64" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F64" s="6" t="s">
+      <c r="F64" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="1">
         <v>11</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="H64" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I64" s="6">
+      <c r="I64" s="1">
         <v>6</v>
       </c>
-      <c r="J64" s="6">
+      <c r="J64" s="1">
         <v>6</v>
       </c>
-      <c r="K64" s="6" t="s">
+      <c r="K64" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L64" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M64" s="9">
-        <v>90</v>
-      </c>
-      <c r="N64" s="6" t="s">
+      <c r="L64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M64" s="2">
+        <v>90</v>
+      </c>
+      <c r="N64" s="1" t="s">
         <v>188</v>
       </c>
       <c r="O64" s="1"/>
     </row>
     <row r="65" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="8">
+      <c r="A65" s="7">
         <v>45929</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D65" s="6" t="s">
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="1">
         <v>7</v>
       </c>
-      <c r="H65" s="6" t="s">
+      <c r="H65" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I65" s="6">
-        <v>4</v>
-      </c>
-      <c r="J65" s="6">
-        <v>4</v>
-      </c>
-      <c r="K65" s="6" t="s">
+      <c r="I65" s="1">
+        <v>4</v>
+      </c>
+      <c r="J65" s="1">
+        <v>4</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="L65" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M65" s="9">
-        <v>90</v>
-      </c>
-      <c r="N65" s="6" t="s">
+      <c r="L65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M65" s="2">
+        <v>90</v>
+      </c>
+      <c r="N65" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O65" s="2"/>
     </row>
     <row r="66" spans="1:15" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="8">
+      <c r="A66" s="7">
         <v>45929</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C66" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D66" s="6" t="s">
+      <c r="C66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="1">
         <v>10</v>
       </c>
-      <c r="H66" s="6" t="s">
+      <c r="H66" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I66" s="6">
-        <v>4</v>
-      </c>
-      <c r="J66" s="6">
-        <v>5</v>
-      </c>
-      <c r="K66" s="6" t="s">
+      <c r="I66" s="1">
+        <v>4</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L66" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M66" s="9">
-        <v>90</v>
-      </c>
-      <c r="N66" s="6" t="s">
+      <c r="L66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M66" s="2">
+        <v>90</v>
+      </c>
+      <c r="N66" s="1" t="s">
         <v>37</v>
       </c>
       <c r="O66" s="2"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A67" s="10" t="s">
+      <c r="A67" t="s">
         <v>189</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67" s="10" t="s">
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
         <v>190</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" t="s">
         <v>191</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" t="s">
         <v>192</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G67">
         <v>16</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" t="s">
         <v>16</v>
       </c>
-      <c r="I67" s="10">
-        <v>5</v>
-      </c>
-      <c r="J67" s="10">
-        <v>4</v>
-      </c>
-      <c r="K67" s="10" t="s">
+      <c r="I67">
+        <v>5</v>
+      </c>
+      <c r="J67">
+        <v>4</v>
+      </c>
+      <c r="K67" t="s">
         <v>193</v>
       </c>
-      <c r="L67" s="10" t="s">
+      <c r="L67" t="s">
         <v>194</v>
       </c>
-      <c r="M67" s="10">
-        <v>90</v>
-      </c>
-      <c r="N67" s="6" t="s">
+      <c r="M67">
+        <v>90</v>
+      </c>
+      <c r="N67" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A68" s="10" t="s">
+      <c r="A68" t="s">
         <v>189</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D68" s="10" t="s">
+      <c r="B68" t="s">
+        <v>21</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
         <v>190</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" t="s">
         <v>191</v>
       </c>
-      <c r="F68" s="10" t="s">
+      <c r="F68" t="s">
         <v>195</v>
       </c>
-      <c r="G68" s="10">
-        <v>5</v>
-      </c>
-      <c r="H68" s="10" t="s">
+      <c r="G68">
+        <v>5</v>
+      </c>
+      <c r="H68" t="s">
         <v>78</v>
       </c>
-      <c r="I68" s="10">
-        <v>4</v>
-      </c>
-      <c r="J68" s="10">
-        <v>5</v>
-      </c>
-      <c r="K68" s="10" t="s">
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68" t="s">
         <v>196</v>
       </c>
-      <c r="L68" s="10" t="s">
+      <c r="L68" t="s">
         <v>194</v>
       </c>
-      <c r="M68" s="10">
-        <v>90</v>
-      </c>
-      <c r="N68" s="6" t="s">
+      <c r="M68">
+        <v>90</v>
+      </c>
+      <c r="N68" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A69" s="10" t="s">
+      <c r="A69" t="s">
         <v>189</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D69" s="10" t="s">
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" t="s">
         <v>191</v>
       </c>
-      <c r="F69" s="10" t="s">
+      <c r="F69" t="s">
         <v>197</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69">
         <v>8</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" t="s">
         <v>20</v>
       </c>
-      <c r="I69" s="10">
-        <v>4</v>
-      </c>
-      <c r="J69" s="10">
-        <v>4</v>
-      </c>
-      <c r="K69" s="10" t="s">
+      <c r="I69">
+        <v>4</v>
+      </c>
+      <c r="J69">
+        <v>4</v>
+      </c>
+      <c r="K69" t="s">
         <v>198</v>
       </c>
-      <c r="L69" s="10" t="s">
+      <c r="L69" t="s">
         <v>194</v>
       </c>
-      <c r="M69" s="10">
+      <c r="M69">
         <v>80</v>
       </c>
-      <c r="N69" s="6" t="s">
+      <c r="N69" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A70" s="10" t="s">
+      <c r="A70" t="s">
         <v>189</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D70" s="10" t="s">
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
         <v>190</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" t="s">
         <v>191</v>
       </c>
-      <c r="F70" s="10" t="s">
+      <c r="F70" t="s">
         <v>199</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70">
         <v>20</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" t="s">
         <v>27</v>
       </c>
-      <c r="I70" s="10">
-        <v>4</v>
-      </c>
-      <c r="J70" s="10">
-        <v>4</v>
-      </c>
-      <c r="K70" s="10" t="s">
+      <c r="I70">
+        <v>4</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70" t="s">
         <v>200</v>
       </c>
-      <c r="L70" s="10" t="s">
+      <c r="L70" t="s">
         <v>194</v>
       </c>
-      <c r="M70" s="10">
+      <c r="M70">
         <v>70</v>
       </c>
-      <c r="N70" s="6" t="s">
+      <c r="N70" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A71" s="10" t="s">
+      <c r="A71" t="s">
         <v>189</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" s="10" t="s">
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
         <v>190</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" t="s">
         <v>191</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F71" t="s">
         <v>201</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G71">
         <v>10</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" t="s">
         <v>18</v>
       </c>
-      <c r="I71" s="10">
-        <v>4</v>
-      </c>
-      <c r="J71" s="10">
-        <v>5</v>
-      </c>
-      <c r="K71" s="10" t="s">
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71">
+        <v>5</v>
+      </c>
+      <c r="K71" t="s">
         <v>202</v>
       </c>
-      <c r="L71" s="10" t="s">
+      <c r="L71" t="s">
         <v>194</v>
       </c>
-      <c r="M71" s="10">
-        <v>90</v>
-      </c>
-      <c r="N71" s="6" t="s">
+      <c r="M71">
+        <v>90</v>
+      </c>
+      <c r="N71" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A72" s="10" t="s">
+      <c r="A72" t="s">
         <v>189</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="10" t="s">
+      <c r="B72" t="s">
+        <v>21</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
         <v>190</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" t="s">
         <v>203</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" t="s">
         <v>204</v>
       </c>
-      <c r="G72" s="10">
+      <c r="G72">
         <v>11</v>
       </c>
-      <c r="H72" s="10" t="s">
+      <c r="H72" t="s">
         <v>75</v>
       </c>
-      <c r="I72" s="10">
-        <v>4</v>
-      </c>
-      <c r="J72" s="10">
-        <v>4</v>
-      </c>
-      <c r="K72" s="10" t="s">
+      <c r="I72">
+        <v>4</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72" t="s">
         <v>205</v>
       </c>
-      <c r="L72" s="10" t="s">
+      <c r="L72" t="s">
         <v>194</v>
       </c>
-      <c r="M72" s="10">
+      <c r="M72">
         <v>87</v>
       </c>
-      <c r="N72" s="6" t="s">
+      <c r="N72" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A73" s="10" t="s">
+      <c r="A73" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D73" s="10" t="s">
+      <c r="B73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
         <v>190</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" t="s">
         <v>203</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" t="s">
         <v>206</v>
       </c>
-      <c r="G73" s="10">
+      <c r="G73">
         <v>2</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" t="s">
         <v>78</v>
       </c>
-      <c r="I73" s="10">
+      <c r="I73">
         <v>3</v>
       </c>
-      <c r="J73" s="10">
-        <v>4</v>
-      </c>
-      <c r="K73" s="10" t="s">
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73" t="s">
         <v>207</v>
       </c>
-      <c r="L73" s="10" t="s">
+      <c r="L73" t="s">
         <v>194</v>
       </c>
-      <c r="M73" s="10">
-        <v>90</v>
-      </c>
-      <c r="N73" s="6" t="s">
+      <c r="M73">
+        <v>90</v>
+      </c>
+      <c r="N73" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A74" s="10" t="s">
+      <c r="A74" t="s">
         <v>189</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
         <v>190</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" t="s">
         <v>203</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F74" t="s">
         <v>208</v>
       </c>
-      <c r="G74" s="10">
+      <c r="G74">
         <v>6</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H74" t="s">
         <v>20</v>
       </c>
-      <c r="I74" s="10">
-        <v>5</v>
-      </c>
-      <c r="J74" s="10">
-        <v>5</v>
-      </c>
-      <c r="K74" s="10" t="s">
+      <c r="I74">
+        <v>5</v>
+      </c>
+      <c r="J74">
+        <v>5</v>
+      </c>
+      <c r="K74" t="s">
         <v>209</v>
       </c>
-      <c r="L74" s="10" t="s">
+      <c r="L74" t="s">
         <v>194</v>
       </c>
-      <c r="M74" s="10">
-        <v>90</v>
-      </c>
-      <c r="N74" s="6" t="s">
+      <c r="M74">
+        <v>90</v>
+      </c>
+      <c r="N74" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A75" s="10" t="s">
+      <c r="A75" t="s">
         <v>189</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="B75" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
         <v>190</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" t="s">
         <v>203</v>
       </c>
-      <c r="F75" s="10" t="s">
+      <c r="F75" t="s">
         <v>210</v>
       </c>
-      <c r="G75" s="10">
+      <c r="G75">
         <v>7</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" t="s">
         <v>46</v>
       </c>
-      <c r="I75" s="10">
+      <c r="I75">
         <v>3</v>
       </c>
-      <c r="J75" s="10">
-        <v>4</v>
-      </c>
-      <c r="K75" s="10" t="s">
+      <c r="J75">
+        <v>4</v>
+      </c>
+      <c r="K75" t="s">
         <v>211</v>
       </c>
-      <c r="L75" s="10" t="s">
+      <c r="L75" t="s">
         <v>194</v>
       </c>
-      <c r="M75" s="10">
+      <c r="M75">
         <v>65</v>
       </c>
-      <c r="N75" s="6" t="s">
+      <c r="N75" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A76" s="10" t="s">
+      <c r="A76" t="s">
         <v>189</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D76" s="10" t="s">
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
         <v>190</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" t="s">
         <v>203</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" t="s">
         <v>212</v>
       </c>
-      <c r="G76" s="10">
+      <c r="G76">
         <v>20</v>
       </c>
-      <c r="H76" s="10" t="s">
+      <c r="H76" t="s">
         <v>18</v>
       </c>
-      <c r="I76" s="10">
-        <v>5</v>
-      </c>
-      <c r="J76" s="10">
-        <v>5</v>
-      </c>
-      <c r="K76" s="10" t="s">
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+      <c r="K76" t="s">
         <v>213</v>
       </c>
-      <c r="L76" s="10" t="s">
+      <c r="L76" t="s">
         <v>194</v>
       </c>
-      <c r="M76" s="10">
+      <c r="M76">
         <v>74</v>
       </c>
-      <c r="N76" s="6" t="s">
+      <c r="N76" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A77" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G77" s="1">
+        <v>3</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I77" s="1">
+        <v>4</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M77" s="2">
+        <v>90</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G78" s="1">
+        <v>12</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="1">
+        <v>4</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="M78" s="2">
+        <v>90</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A79" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="G79" s="1">
+        <v>7</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I79" s="1">
+        <v>4</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M79" s="2">
+        <v>90</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="A80" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G80" s="1">
+        <v>9</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I80" s="1">
+        <v>4</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M80" s="2">
+        <v>90</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A81" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G81" s="1">
+        <v>17</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I81" s="1">
+        <v>4</v>
+      </c>
+      <c r="J81" s="1">
+        <v>4</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="L81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M81" s="2">
+        <v>90</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="1">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1">
+        <v>4</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M82" s="2">
+        <v>90</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A83" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G83" s="1">
+        <v>5</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="1">
+        <v>3</v>
+      </c>
+      <c r="J83" s="1">
+        <v>4</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M83" s="2">
+        <v>90</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G84" s="1">
+        <v>7</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I84" s="1">
+        <v>5</v>
+      </c>
+      <c r="J84" s="1">
+        <v>4</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M84" s="2">
+        <v>90</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I85" s="1">
+        <v>4</v>
+      </c>
+      <c r="J85" s="1">
+        <v>3</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M85" s="2">
+        <v>90</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="7">
+        <v>45933</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G86" s="1">
+        <v>9</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I86" s="1">
+        <v>5</v>
+      </c>
+      <c r="J86" s="1">
+        <v>4</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N86" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/fifa_u20_player_reports.xlsx
+++ b/fifa_u20_player_reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvarolopezmolina/Desktop/alnassracademy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75693651-EA17-ED40-83FA-BC08634403D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387317E3-6D8C-844E-AEDA-A906F53EE6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -535,9 +535,6 @@
     <t>Box-to-box midfielder with size and structure, effective carrying the ball and breaking lines with passes. Showed energy, composure and capacity to shoot from distance. Alongside Gilberto, one of the most influential players for Mexico.</t>
   </si>
   <si>
-    <t>Elías Montiel</t>
-  </si>
-  <si>
     <t>Nominally wide in a 3-4-2-1 but inverted into central areas in possession. Dynamic, with good passing tempo, composure on the ball and tactical discipline. Strong in duels and competitive, offering balance between defensive work and creative support.</t>
   </si>
   <si>
@@ -794,13 +791,16 @@
   <si>
     <t>L. Olmeta</t>
   </si>
+  <si>
+    <t>Elias Montiel</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -857,7 +857,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2690,7 +2690,7 @@
         <v>96</v>
       </c>
       <c r="F33" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G33">
         <v>11</v>
@@ -2734,7 +2734,7 @@
         <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G34">
         <v>3</v>
@@ -3154,7 +3154,7 @@
         <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4091,7 +4091,7 @@
         <v>162</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="G63">
         <v>8</v>
@@ -4106,7 +4106,7 @@
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L63" t="s">
         <v>23</v>
@@ -4135,7 +4135,7 @@
         <v>162</v>
       </c>
       <c r="F64" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G64">
         <v>11</v>
@@ -4150,16 +4150,16 @@
         <v>6</v>
       </c>
       <c r="K64" t="s">
+        <v>173</v>
+      </c>
+      <c r="L64" t="s">
+        <v>23</v>
+      </c>
+      <c r="M64">
+        <v>90</v>
+      </c>
+      <c r="N64" t="s">
         <v>174</v>
-      </c>
-      <c r="L64" t="s">
-        <v>23</v>
-      </c>
-      <c r="M64">
-        <v>90</v>
-      </c>
-      <c r="N64" t="s">
-        <v>175</v>
       </c>
       <c r="P64">
         <v>2008</v>
@@ -4182,7 +4182,7 @@
         <v>162</v>
       </c>
       <c r="F65" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G65">
         <v>7</v>
@@ -4197,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="K65" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L65" t="s">
         <v>23</v>
@@ -4229,7 +4229,7 @@
         <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G66">
         <v>10</v>
@@ -4244,7 +4244,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L66" t="s">
         <v>23</v>
@@ -4261,22 +4261,22 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
         <v>180</v>
       </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>181</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>182</v>
-      </c>
-      <c r="F67" t="s">
-        <v>183</v>
       </c>
       <c r="G67">
         <v>16</v>
@@ -4291,10 +4291,10 @@
         <v>4</v>
       </c>
       <c r="K67" t="s">
+        <v>183</v>
+      </c>
+      <c r="L67" t="s">
         <v>184</v>
-      </c>
-      <c r="L67" t="s">
-        <v>185</v>
       </c>
       <c r="M67">
         <v>90</v>
@@ -4308,22 +4308,22 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
         <v>180</v>
       </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>181</v>
       </c>
-      <c r="E68" t="s">
-        <v>182</v>
-      </c>
       <c r="F68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G68">
         <v>5</v>
@@ -4338,10 +4338,10 @@
         <v>5</v>
       </c>
       <c r="K68" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M68">
         <v>90</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>179</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
         <v>180</v>
       </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>181</v>
       </c>
-      <c r="E69" t="s">
-        <v>182</v>
-      </c>
       <c r="F69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G69">
         <v>8</v>
@@ -4385,10 +4385,10 @@
         <v>4</v>
       </c>
       <c r="K69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M69">
         <v>80</v>
@@ -4402,22 +4402,22 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>179</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
         <v>180</v>
       </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>181</v>
       </c>
-      <c r="E70" t="s">
-        <v>182</v>
-      </c>
       <c r="F70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G70">
         <v>20</v>
@@ -4432,10 +4432,10 @@
         <v>4</v>
       </c>
       <c r="K70" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M70">
         <v>70</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>179</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
         <v>180</v>
       </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>181</v>
       </c>
-      <c r="E71" t="s">
-        <v>182</v>
-      </c>
       <c r="F71" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G71">
         <v>10</v>
@@ -4479,10 +4479,10 @@
         <v>5</v>
       </c>
       <c r="K71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M71">
         <v>90</v>
@@ -4496,22 +4496,22 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>179</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
         <v>180</v>
       </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" t="s">
-        <v>181</v>
-      </c>
       <c r="E72" t="s">
+        <v>193</v>
+      </c>
+      <c r="F72" t="s">
         <v>194</v>
-      </c>
-      <c r="F72" t="s">
-        <v>195</v>
       </c>
       <c r="G72">
         <v>11</v>
@@ -4526,10 +4526,10 @@
         <v>4</v>
       </c>
       <c r="K72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M72">
         <v>87</v>
@@ -4543,22 +4543,22 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>179</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" t="s">
         <v>180</v>
       </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" t="s">
-        <v>181</v>
-      </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -4573,10 +4573,10 @@
         <v>4</v>
       </c>
       <c r="K73" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M73">
         <v>90</v>
@@ -4590,22 +4590,22 @@
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>179</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" t="s">
         <v>180</v>
       </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" t="s">
-        <v>181</v>
-      </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F74" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G74">
         <v>6</v>
@@ -4620,10 +4620,10 @@
         <v>5</v>
       </c>
       <c r="K74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M74">
         <v>90</v>
@@ -4637,22 +4637,22 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" t="s">
         <v>180</v>
       </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="s">
-        <v>17</v>
-      </c>
-      <c r="D75" t="s">
-        <v>181</v>
-      </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F75" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G75">
         <v>7</v>
@@ -4667,10 +4667,10 @@
         <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M75">
         <v>65</v>
@@ -4684,22 +4684,22 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" t="s">
         <v>180</v>
       </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="s">
-        <v>17</v>
-      </c>
-      <c r="D76" t="s">
-        <v>181</v>
-      </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G76">
         <v>20</v>
@@ -4714,10 +4714,10 @@
         <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L76" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M76">
         <v>74</v>
@@ -4740,13 +4740,13 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E77" t="s">
         <v>106</v>
       </c>
       <c r="F77" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G77">
         <v>3</v>
@@ -4761,7 +4761,7 @@
         <v>4</v>
       </c>
       <c r="K77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L77" t="s">
         <v>23</v>
@@ -4787,13 +4787,13 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E78" t="s">
         <v>106</v>
       </c>
       <c r="F78" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G78">
         <v>12</v>
@@ -4808,10 +4808,10 @@
         <v>4</v>
       </c>
       <c r="K78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M78">
         <v>90</v>
@@ -4834,13 +4834,13 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E79" t="s">
         <v>106</v>
       </c>
       <c r="F79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G79">
         <v>7</v>
@@ -4855,7 +4855,7 @@
         <v>4</v>
       </c>
       <c r="K79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L79" t="s">
         <v>23</v>
@@ -4881,7 +4881,7 @@
         <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E80" t="s">
         <v>106</v>
@@ -4902,7 +4902,7 @@
         <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L80" t="s">
         <v>23</v>
@@ -4928,7 +4928,7 @@
         <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E81" t="s">
         <v>106</v>
@@ -4949,7 +4949,7 @@
         <v>4</v>
       </c>
       <c r="K81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L81" t="s">
         <v>23</v>
@@ -4975,13 +4975,13 @@
         <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E82" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" t="s">
         <v>214</v>
-      </c>
-      <c r="F82" t="s">
-        <v>215</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4996,7 +4996,7 @@
         <v>4</v>
       </c>
       <c r="K82" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L82" t="s">
         <v>23</v>
@@ -5022,13 +5022,13 @@
         <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G83">
         <v>5</v>
@@ -5043,7 +5043,7 @@
         <v>4</v>
       </c>
       <c r="K83" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L83" t="s">
         <v>23</v>
@@ -5069,13 +5069,13 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F84" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G84">
         <v>7</v>
@@ -5090,7 +5090,7 @@
         <v>4</v>
       </c>
       <c r="K84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L84" t="s">
         <v>23</v>
@@ -5116,13 +5116,13 @@
         <v>17</v>
       </c>
       <c r="D85" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E85" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G85">
         <v>10</v>
@@ -5137,7 +5137,7 @@
         <v>3</v>
       </c>
       <c r="K85" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L85" t="s">
         <v>23</v>
@@ -5163,13 +5163,13 @@
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G86">
         <v>9</v>
@@ -5184,7 +5184,7 @@
         <v>4</v>
       </c>
       <c r="K86" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L86" t="s">
         <v>34</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>224</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" t="s">
         <v>225</v>
       </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" t="s">
-        <v>226</v>
-      </c>
       <c r="E87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -5231,7 +5231,7 @@
         <v>5</v>
       </c>
       <c r="K87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L87" t="s">
         <v>23</v>
@@ -5240,7 +5240,7 @@
         <v>90</v>
       </c>
       <c r="N87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O87">
         <v>2005</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>224</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" t="s">
         <v>225</v>
       </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" t="s">
-        <v>226</v>
-      </c>
       <c r="E88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F88" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G88">
         <v>8</v>
@@ -5281,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L88" t="s">
         <v>23</v>
@@ -5301,22 +5301,22 @@
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>224</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" t="s">
         <v>225</v>
       </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" t="s">
-        <v>226</v>
-      </c>
       <c r="E89" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F89" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G89">
         <v>2</v>
@@ -5331,7 +5331,7 @@
         <v>4</v>
       </c>
       <c r="K89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L89" t="s">
         <v>23</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>224</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" t="s">
         <v>225</v>
       </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="s">
-        <v>17</v>
-      </c>
-      <c r="D90" t="s">
-        <v>226</v>
-      </c>
       <c r="E90" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F90" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G90">
         <v>11</v>
@@ -5381,7 +5381,7 @@
         <v>4</v>
       </c>
       <c r="K90" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L90" t="s">
         <v>23</v>
@@ -5401,22 +5401,22 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" t="s">
         <v>225</v>
       </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" t="s">
-        <v>226</v>
-      </c>
       <c r="E91" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F91" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G91">
         <v>15</v>
@@ -5431,7 +5431,7 @@
         <v>5</v>
       </c>
       <c r="K91" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L91" t="s">
         <v>23</v>
@@ -5451,22 +5451,22 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>224</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" t="s">
         <v>225</v>
       </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="s">
-        <v>17</v>
-      </c>
-      <c r="D92" t="s">
-        <v>226</v>
-      </c>
       <c r="E92" t="s">
+        <v>234</v>
+      </c>
+      <c r="F92" t="s">
         <v>235</v>
-      </c>
-      <c r="F92" t="s">
-        <v>236</v>
       </c>
       <c r="G92">
         <v>9</v>
@@ -5481,7 +5481,7 @@
         <v>4</v>
       </c>
       <c r="K92" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L92" t="s">
         <v>23</v>
@@ -5501,22 +5501,22 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>224</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" t="s">
         <v>225</v>
       </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" t="s">
-        <v>226</v>
-      </c>
       <c r="E93" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F93" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G93">
         <v>14</v>
@@ -5531,7 +5531,7 @@
         <v>4</v>
       </c>
       <c r="K93" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L93" t="s">
         <v>23</v>
@@ -5551,22 +5551,22 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>224</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" t="s">
         <v>225</v>
       </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="s">
-        <v>17</v>
-      </c>
-      <c r="D94" t="s">
-        <v>226</v>
-      </c>
       <c r="E94" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G94">
         <v>10</v>
@@ -5581,7 +5581,7 @@
         <v>5</v>
       </c>
       <c r="K94" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L94" t="s">
         <v>23</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B95" t="s">
         <v>16</v>
@@ -5610,13 +5610,13 @@
         <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E95" t="s">
         <v>162</v>
       </c>
       <c r="F95" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G95">
         <v>15</v>
@@ -5631,7 +5631,7 @@
         <v>4</v>
       </c>
       <c r="K95" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L95" t="s">
         <v>23</v>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B96" t="s">
         <v>16</v>
@@ -5660,13 +5660,13 @@
         <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E96" t="s">
         <v>162</v>
       </c>
       <c r="F96" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G96">
         <v>10</v>
@@ -5681,7 +5681,7 @@
         <v>4</v>
       </c>
       <c r="K96" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L96" t="s">
         <v>23</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B97" t="s">
         <v>16</v>
@@ -5710,13 +5710,13 @@
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E97" t="s">
         <v>162</v>
       </c>
       <c r="F97" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G97">
         <v>11</v>
@@ -5731,7 +5731,7 @@
         <v>5</v>
       </c>
       <c r="K97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L97" t="s">
         <v>23</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
@@ -5760,13 +5760,13 @@
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E98" t="s">
         <v>71</v>
       </c>
       <c r="F98" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G98">
         <v>9</v>
@@ -5781,7 +5781,7 @@
         <v>4</v>
       </c>
       <c r="K98" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L98" t="s">
         <v>23</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
@@ -5810,13 +5810,13 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E99" t="s">
         <v>162</v>
       </c>
       <c r="F99" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G99">
         <v>17</v>
@@ -5831,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="K99" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L99" t="s">
         <v>23</v>
